--- a/input/New_Vehicle_Delivery_Experience.xlsx
+++ b/input/New_Vehicle_Delivery_Experience.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OMEN\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sales Audit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB289CB6-32D3-4AD1-9D76-166A2D1CC132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9643A7DC-2C49-45B9-BF4E-D128119E80CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t>Zone</t>
   </si>
@@ -67,182 +67,49 @@
     <t>KHOTHRUD</t>
   </si>
   <si>
-    <t>VDN27J000197</t>
-  </si>
-  <si>
-    <t>CF2700153920</t>
+    <t>VDN27J000258</t>
+  </si>
+  <si>
+    <t>CF2700192411</t>
+  </si>
+  <si>
+    <t>SCORPIO-N</t>
+  </si>
+  <si>
+    <t>Misinformation about delivery status;No Updates given on Vehicle delivery status;Sales Consultant did not explain vehicle features</t>
+  </si>
+  <si>
+    <t>Received delay.  No proper communication from dealer team for the same. No test ride provided.</t>
+  </si>
+  <si>
+    <t>AKASH BALU RATHOD</t>
+  </si>
+  <si>
+    <t>13MS1564</t>
+  </si>
+  <si>
+    <t>CHANDAN NAGAR_CUBE</t>
+  </si>
+  <si>
+    <t>VDN27Q000559</t>
+  </si>
+  <si>
+    <t>CF2700193522</t>
   </si>
   <si>
     <t>XUV 7XO</t>
   </si>
   <si>
-    <t>Dealership Amenities not satisfactory;Other;Sales Consultant did not explain vehicle features</t>
-  </si>
-  <si>
-    <t>Delivey delay, Cleanliness</t>
-  </si>
-  <si>
-    <t>ANIKET HEMANT PORE</t>
-  </si>
-  <si>
-    <t>13MS1685</t>
-  </si>
-  <si>
-    <t>MANJHARI_SH</t>
-  </si>
-  <si>
-    <t>VDN27N000187</t>
-  </si>
-  <si>
-    <t>CF2700156466</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>SOMESH MOHAN DAUNDKAR</t>
-  </si>
-  <si>
-    <t>13LR4861</t>
-  </si>
-  <si>
-    <t>VDN27J000209</t>
-  </si>
-  <si>
-    <t>CF2700159111</t>
-  </si>
-  <si>
-    <t>NEW THAR</t>
-  </si>
-  <si>
-    <t>Misinformation about delivery status;No Updates given on Vehicle delivery status;Other</t>
-  </si>
-  <si>
-    <t>The GM is not at all supportive and did a lot of miscommunication and fake promises about the delivery of the vehicle.</t>
-  </si>
-  <si>
-    <t>ASHWINI SACHIN TUPE</t>
-  </si>
-  <si>
-    <t>13OU9400</t>
-  </si>
-  <si>
-    <t>VDN27J000219</t>
-  </si>
-  <si>
-    <t>CF2700165274</t>
-  </si>
-  <si>
-    <t>XUV3XO</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>1. VDN punch not completed still after several days:Despite the car being delivered on 5 August, the VDN punch was not completed until 13 August. As a result, when I approached the service centre, my vehicle was not even visible in their system. This is a serious coordination failure and caused unnecessary inconvenience to me as a customer.
-2. Booking amount refund: My car was delivered on 5 August, and financial transactions were done way earlier, it was promised to refund asap but on 11 Aug showroom is asking for cheque leaf with customer name , can’t this be identified earler on the time of submission? still have concerns regarding the refund of the ?21,000 booking amount. I do not understand why the refund was not processed on the day of delivery, or why it is taking so long, they also denied to add this amount in car purchase value this is total harassment. 
-3. Number plate holder: The number plate was being installed without a proper border holder, without even asking , as a resu</t>
-  </si>
-  <si>
-    <t>UNNATI MOTORS, A DIVISION OF MICROPARK LOGISTICS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>WAGHOLI_3S</t>
-  </si>
-  <si>
-    <t>VDN27F001395</t>
-  </si>
-  <si>
-    <t>CF2700171833</t>
-  </si>
-  <si>
-    <t>SCORPIO-N</t>
-  </si>
-  <si>
-    <t>AKSHAY BABURAV KAMBLE</t>
-  </si>
-  <si>
-    <t>13NT8685</t>
-  </si>
-  <si>
-    <t>GREAT_NAG_ROAD</t>
-  </si>
-  <si>
-    <t>VDN270000277</t>
-  </si>
-  <si>
-    <t>CF2700180594</t>
-  </si>
-  <si>
-    <t>PRAVIN DHARMARAJ PARDHI</t>
-  </si>
-  <si>
-    <t>13RX1902</t>
-  </si>
-  <si>
-    <t>AMRAVATI</t>
-  </si>
-  <si>
-    <t>VDN27B000311</t>
-  </si>
-  <si>
-    <t>CF2700174595</t>
-  </si>
-  <si>
     <t>Poor vehicle condition and cleanliness</t>
   </si>
   <si>
-    <t>Technical issue, car break  down in th middle of road</t>
-  </si>
-  <si>
-    <t>SURAJ PRAKASH YADAV</t>
-  </si>
-  <si>
-    <t>13MS3260</t>
-  </si>
-  <si>
-    <t>SHIKRAPUR_SZS</t>
-  </si>
-  <si>
-    <t>VDN27L000034</t>
-  </si>
-  <si>
-    <t>CF2700175947</t>
-  </si>
-  <si>
-    <t>Dealership Amenities not satisfactory</t>
-  </si>
-  <si>
-    <t>Even at the time of delivery, the vehicle was not properly cleaned, and we had to ask the dealership to clean it.
-The dealership has still not activated my Roadside Assistance (RSA). My Extended Warranty has also not been activated yet. It has been 15 days since I took delivery, but I still have not received any update.
-Additionally, the dealership entered my email ID incorrectly, and it has still not been corrected.</t>
-  </si>
-  <si>
-    <t>VAIBHAV GAJANAN WAYGUDAGHE</t>
-  </si>
-  <si>
-    <t>13PV7633</t>
-  </si>
-  <si>
-    <t>NAGPUR_KAMPTHEE ROAD</t>
-  </si>
-  <si>
-    <t>VDN27A000675</t>
-  </si>
-  <si>
-    <t>CF2700179177</t>
-  </si>
-  <si>
-    <t>No Updates given on Vehicle delivery status;Poor vehicle condition and cleanliness;Sales Consultant did not explain vehicle features;Unhappy with Ceremonial Delivery Moment</t>
-  </si>
-  <si>
-    <t>Lack of communication as well as misguide</t>
-  </si>
-  <si>
-    <t>KARTIK NARAYAN HATWAR</t>
-  </si>
-  <si>
-    <t>13FL6733</t>
+    <t>They provided the car with too many defects.</t>
+  </si>
+  <si>
+    <t>MONISH MAHADEO MHASKE</t>
+  </si>
+  <si>
+    <t>13PV0455</t>
   </si>
 </sst>
 </file>
@@ -614,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -707,264 +574,19 @@
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" t="s">
         <v>29</v>
-      </c>
-      <c r="G4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" t="s">
-        <v>45</v>
-      </c>
-      <c r="K6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" t="s">
-        <v>50</v>
-      </c>
-      <c r="K7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" t="s">
-        <v>55</v>
-      </c>
-      <c r="I8" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I9" t="s">
-        <v>63</v>
-      </c>
-      <c r="J9" t="s">
-        <v>64</v>
-      </c>
-      <c r="K9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" t="s">
-        <v>67</v>
-      </c>
-      <c r="F10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" t="s">
-        <v>70</v>
-      </c>
-      <c r="J10" t="s">
-        <v>71</v>
-      </c>
-      <c r="K10" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
